--- a/product-definitions/spreadsheet/boundary-layer-temperature-profiles.xlsx
+++ b/product-definitions/spreadsheet/boundary-layer-temperature-profiles.xlsx
@@ -299,7 +299,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -329,11 +329,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -350,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -377,13 +372,13 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -395,19 +390,18 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1881,7 +1875,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="6" t="s">
         <v>20</v>
       </c>
@@ -1889,7 +1883,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="6" t="s">
         <v>22</v>
       </c>
@@ -1897,7 +1891,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="6" t="s">
         <v>31</v>
       </c>
@@ -1905,7 +1899,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="6" t="s">
         <v>24</v>
       </c>
@@ -1913,10 +1907,10 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="C25" s="8"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="12" t="s">
         <v>33</v>
       </c>
@@ -1926,7 +1920,7 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
         <v>11</v>
@@ -1938,7 +1932,7 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
         <v>13</v>
@@ -1950,7 +1944,7 @@
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
         <v>2</v>
@@ -1962,7 +1956,7 @@
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
         <v>14</v>
@@ -1972,7 +1966,7 @@
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="10" t="s">
         <v>15</v>
@@ -1984,7 +1978,7 @@
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="10" t="s">
         <v>37</v>
@@ -1996,7 +1990,7 @@
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="18" t="s">
         <v>39</v>
@@ -2008,7 +2002,7 @@
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="16"/>
@@ -2016,7 +2010,7 @@
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="12" t="s">
         <v>41</v>
       </c>
@@ -2026,7 +2020,7 @@
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="B36" s="10" t="s">
         <v>11</v>
@@ -2038,7 +2032,7 @@
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="10" t="s">
         <v>13</v>
@@ -2050,7 +2044,7 @@
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="10" t="s">
         <v>2</v>
@@ -2062,7 +2056,7 @@
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="10" t="s">
         <v>14</v>
@@ -2072,7 +2066,7 @@
       <c r="E39" s="10"/>
       <c r="F39" s="10"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="10" t="s">
         <v>15</v>
@@ -2084,7 +2078,7 @@
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="B41" s="10" t="s">
         <v>37</v>
@@ -2096,7 +2090,7 @@
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="18" t="s">
         <v>39</v>
@@ -2108,7 +2102,7 @@
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="16"/>
@@ -2116,7 +2110,7 @@
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="12" t="s">
         <v>45</v>
       </c>
@@ -2126,7 +2120,7 @@
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="10" t="s">
         <v>11</v>
@@ -2138,7 +2132,7 @@
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="10" t="s">
         <v>13</v>
@@ -2150,7 +2144,7 @@
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="10" t="s">
         <v>2</v>
@@ -2162,7 +2156,7 @@
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="10" t="s">
         <v>14</v>
@@ -2172,7 +2166,7 @@
       <c r="E48" s="10"/>
       <c r="F48" s="10"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="10" t="s">
         <v>15</v>
@@ -2184,7 +2178,7 @@
       <c r="E49" s="10"/>
       <c r="F49" s="10"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="10" t="s">
         <v>37</v>
@@ -2196,7 +2190,7 @@
       <c r="E50" s="10"/>
       <c r="F50" s="10"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="18" t="s">
         <v>39</v>
@@ -2208,16 +2202,16 @@
       <c r="E51" s="10"/>
       <c r="F51" s="10"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="C52" s="8"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C53" s="8"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="B54" s="6" t="s">
         <v>11</v>
       </c>
@@ -2225,7 +2219,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="B55" s="6" t="s">
         <v>13</v>
       </c>
@@ -2233,7 +2227,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="B56" s="6" t="s">
         <v>2</v>
       </c>
@@ -2241,13 +2235,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="B57" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C57" s="7"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="B58" s="6" t="s">
         <v>15</v>
       </c>
@@ -2255,7 +2249,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="B59" s="10" t="s">
         <v>37</v>
       </c>
@@ -2263,7 +2257,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="B60" s="18" t="s">
         <v>39</v>
       </c>
@@ -2271,16 +2265,16 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="C61" s="7"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="6" t="s">
         <v>51</v>
       </c>
       <c r="C62" s="8"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="B63" s="6" t="s">
         <v>11</v>
       </c>
@@ -2288,7 +2282,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="B64" s="6" t="s">
         <v>13</v>
       </c>
@@ -2296,7 +2290,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="B65" s="6" t="s">
         <v>2</v>
       </c>
@@ -2304,13 +2298,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="B66" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C66" s="7"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="B67" s="6" t="s">
         <v>15</v>
       </c>
@@ -2318,7 +2312,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="B68" s="10" t="s">
         <v>37</v>
       </c>
@@ -2326,7 +2320,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="B69" s="18" t="s">
         <v>39</v>
       </c>
@@ -2334,16 +2328,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="C70" s="8"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C71" s="8"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="B72" s="6" t="s">
         <v>11</v>
       </c>
@@ -2351,7 +2345,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="B73" s="6" t="s">
         <v>13</v>
       </c>
@@ -2359,7 +2353,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="B74" s="6" t="s">
         <v>2</v>
       </c>
@@ -2367,13 +2361,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="B75" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C75" s="7"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="B76" s="6" t="s">
         <v>15</v>
       </c>
@@ -2381,7 +2375,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="B77" s="10" t="s">
         <v>37</v>
       </c>
@@ -2389,7 +2383,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="B78" s="18" t="s">
         <v>39</v>
       </c>
@@ -2397,16 +2391,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="C79" s="8"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="6" t="s">
         <v>56</v>
       </c>
       <c r="C80" s="8"/>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="B81" s="6" t="s">
         <v>11</v>
       </c>
@@ -2414,7 +2408,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="B82" s="6" t="s">
         <v>13</v>
       </c>
@@ -2422,7 +2416,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="B83" s="6" t="s">
         <v>2</v>
       </c>
@@ -2430,13 +2424,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C84" s="7"/>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="B85" s="6" t="s">
         <v>15</v>
       </c>
@@ -2444,7 +2438,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="B86" s="10" t="s">
         <v>37</v>
       </c>
@@ -2452,7 +2446,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="B87" s="18" t="s">
         <v>39</v>
       </c>
@@ -2460,16 +2454,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="C88" s="8"/>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="6" t="s">
         <v>58</v>
       </c>
       <c r="C89" s="8"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="B90" s="6" t="s">
         <v>11</v>
       </c>
@@ -2477,7 +2471,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="B91" s="6" t="s">
         <v>13</v>
       </c>
@@ -2485,7 +2479,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="B92" s="6" t="s">
         <v>2</v>
       </c>
@@ -2493,13 +2487,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="B93" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C93" s="7"/>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="B94" s="6" t="s">
         <v>15</v>
       </c>
@@ -2507,7 +2501,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="B95" s="10" t="s">
         <v>37</v>
       </c>
@@ -2515,7 +2509,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="B96" s="18" t="s">
         <v>39</v>
       </c>
@@ -2523,16 +2517,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="C97" s="8"/>
     </row>
-    <row r="98">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="6" t="s">
         <v>60</v>
       </c>
       <c r="C98" s="8"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="B99" s="6" t="s">
         <v>11</v>
       </c>
@@ -2540,7 +2534,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="B100" s="6" t="s">
         <v>13</v>
       </c>
@@ -2548,7 +2542,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="B101" s="6" t="s">
         <v>2</v>
       </c>
@@ -2556,13 +2550,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="B102" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C102" s="7"/>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="B103" s="6" t="s">
         <v>15</v>
       </c>
@@ -2570,7 +2564,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="B104" s="10" t="s">
         <v>37</v>
       </c>
@@ -2578,7 +2572,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="B105" s="18" t="s">
         <v>39</v>
       </c>
@@ -2586,16 +2580,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="C106" s="8"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C107" s="8"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="B108" s="6" t="s">
         <v>11</v>
       </c>
@@ -2603,7 +2597,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="B109" s="6" t="s">
         <v>13</v>
       </c>
@@ -2611,7 +2605,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="B110" s="6" t="s">
         <v>2</v>
       </c>
@@ -2619,13 +2613,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="B111" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C111" s="7"/>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="B112" s="6" t="s">
         <v>15</v>
       </c>
@@ -2633,7 +2627,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="B113" s="10" t="s">
         <v>37</v>
       </c>
@@ -2641,7 +2635,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="B114" s="18" t="s">
         <v>39</v>
       </c>
@@ -2649,24 +2643,24 @@
         <v>53</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="C115" s="8"/>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="6" t="s">
         <v>64</v>
       </c>
       <c r="C116" s="8"/>
     </row>
-    <row r="117">
-      <c r="B117" s="20" t="s">
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="B117" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="B118" s="6" t="s">
         <v>13</v>
       </c>
@@ -2674,7 +2668,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="B119" s="6" t="s">
         <v>2</v>
       </c>
@@ -2682,13 +2676,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="B120" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C120" s="7"/>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="B121" s="6" t="s">
         <v>15</v>
       </c>
@@ -2696,7 +2690,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="B122" s="10" t="s">
         <v>37</v>
       </c>
@@ -2704,7 +2698,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="B123" s="18" t="s">
         <v>39</v>
       </c>
@@ -2712,16 +2706,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="C124" s="8"/>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="6" t="s">
         <v>66</v>
       </c>
       <c r="C125" s="8"/>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="B126" s="6" t="s">
         <v>11</v>
       </c>
@@ -2729,7 +2723,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="B127" s="6" t="s">
         <v>13</v>
       </c>
@@ -2737,7 +2731,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="B128" s="6" t="s">
         <v>2</v>
       </c>
@@ -2745,13 +2739,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="B129" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C129" s="7"/>
     </row>
-    <row r="130">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="B130" s="6" t="s">
         <v>15</v>
       </c>
@@ -2759,7 +2753,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="B131" s="10" t="s">
         <v>37</v>
       </c>
@@ -2767,7 +2761,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="B132" s="18" t="s">
         <v>39</v>
       </c>
@@ -2775,16 +2769,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="C133" s="8"/>
     </row>
-    <row r="134">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C134" s="8"/>
     </row>
-    <row r="135">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="B135" s="6" t="s">
         <v>11</v>
       </c>
@@ -2792,7 +2786,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="B136" s="6" t="s">
         <v>13</v>
       </c>
@@ -2800,7 +2794,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="B137" s="6" t="s">
         <v>2</v>
       </c>
@@ -2808,13 +2802,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="B138" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C138" s="7"/>
     </row>
-    <row r="139">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="B139" s="6" t="s">
         <v>15</v>
       </c>
@@ -2822,7 +2816,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="B140" s="10" t="s">
         <v>37</v>
       </c>
@@ -2830,7 +2824,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="B141" s="18" t="s">
         <v>39</v>
       </c>
@@ -2838,16 +2832,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="C142" s="8"/>
     </row>
-    <row r="143">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C143" s="8"/>
     </row>
-    <row r="144">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="B144" s="6" t="s">
         <v>11</v>
       </c>
@@ -2855,7 +2849,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="B145" s="6" t="s">
         <v>13</v>
       </c>
@@ -2863,7 +2857,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" ht="15.75" customHeight="1">
       <c r="B146" s="6" t="s">
         <v>2</v>
       </c>
@@ -2871,13 +2865,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="B147" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C147" s="7"/>
     </row>
-    <row r="148">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="B148" s="6" t="s">
         <v>15</v>
       </c>
@@ -2885,7 +2879,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="B149" s="10" t="s">
         <v>37</v>
       </c>
@@ -2893,7 +2887,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="B150" s="18" t="s">
         <v>39</v>
       </c>
@@ -2901,16 +2895,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="C151" s="8"/>
     </row>
-    <row r="152">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="6" t="s">
         <v>72</v>
       </c>
       <c r="C152" s="8"/>
     </row>
-    <row r="153">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="B153" s="6" t="s">
         <v>11</v>
       </c>
@@ -2918,7 +2912,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="B154" s="6" t="s">
         <v>13</v>
       </c>
@@ -2926,7 +2920,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" ht="15.75" customHeight="1">
       <c r="B155" s="6" t="s">
         <v>2</v>
       </c>
@@ -2934,13 +2928,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="B156" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C156" s="7"/>
     </row>
-    <row r="157">
+    <row r="157" ht="15.75" customHeight="1">
       <c r="B157" s="6" t="s">
         <v>15</v>
       </c>
@@ -2948,7 +2942,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="B158" s="10" t="s">
         <v>37</v>
       </c>
@@ -2956,7 +2950,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="B159" s="18" t="s">
         <v>39</v>
       </c>
@@ -2964,16 +2958,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="C160" s="8"/>
     </row>
-    <row r="161">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="6" t="s">
         <v>74</v>
       </c>
       <c r="C161" s="8"/>
     </row>
-    <row r="162">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="B162" s="6" t="s">
         <v>11</v>
       </c>
@@ -2981,7 +2975,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" ht="15.75" customHeight="1">
       <c r="B163" s="6" t="s">
         <v>13</v>
       </c>
@@ -2989,7 +2983,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" ht="15.75" customHeight="1">
       <c r="B164" s="6" t="s">
         <v>2</v>
       </c>
@@ -2997,13 +2991,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" ht="15.75" customHeight="1">
       <c r="B165" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C165" s="7"/>
     </row>
-    <row r="166">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="B166" s="6" t="s">
         <v>15</v>
       </c>
@@ -3011,7 +3005,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" ht="15.75" customHeight="1">
       <c r="B167" s="10" t="s">
         <v>37</v>
       </c>
@@ -3019,7 +3013,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="B168" s="18" t="s">
         <v>39</v>
       </c>
@@ -3027,16 +3021,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="C169" s="8"/>
     </row>
-    <row r="170">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="6" t="s">
         <v>76</v>
       </c>
       <c r="C170" s="8"/>
     </row>
-    <row r="171">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="B171" s="6" t="s">
         <v>11</v>
       </c>
@@ -3044,7 +3038,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="B172" s="6" t="s">
         <v>13</v>
       </c>
@@ -3052,7 +3046,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" ht="15.75" customHeight="1">
       <c r="B173" s="6" t="s">
         <v>2</v>
       </c>
@@ -3060,13 +3054,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" ht="15.75" customHeight="1">
       <c r="B174" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C174" s="7"/>
     </row>
-    <row r="175">
+    <row r="175" ht="15.75" customHeight="1">
       <c r="B175" s="6" t="s">
         <v>15</v>
       </c>
@@ -3074,7 +3068,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" ht="15.75" customHeight="1">
       <c r="B176" s="10" t="s">
         <v>37</v>
       </c>
@@ -3082,7 +3076,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" ht="15.75" customHeight="1">
       <c r="B177" s="18" t="s">
         <v>39</v>
       </c>
@@ -3090,16 +3084,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" ht="15.75" customHeight="1">
       <c r="C178" s="8"/>
     </row>
-    <row r="179">
+    <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="6" t="s">
         <v>78</v>
       </c>
       <c r="C179" s="8"/>
     </row>
-    <row r="180">
+    <row r="180" ht="15.75" customHeight="1">
       <c r="B180" s="6" t="s">
         <v>11</v>
       </c>
@@ -3107,7 +3101,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" ht="15.75" customHeight="1">
       <c r="B181" s="6" t="s">
         <v>13</v>
       </c>
@@ -3115,7 +3109,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" ht="15.75" customHeight="1">
       <c r="B182" s="6" t="s">
         <v>2</v>
       </c>
@@ -3123,13 +3117,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" ht="15.75" customHeight="1">
       <c r="B183" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C183" s="7"/>
     </row>
-    <row r="184">
+    <row r="184" ht="15.75" customHeight="1">
       <c r="B184" s="6" t="s">
         <v>15</v>
       </c>
@@ -3137,7 +3131,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" ht="15.75" customHeight="1">
       <c r="B185" s="10" t="s">
         <v>37</v>
       </c>
@@ -3145,7 +3139,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" ht="15.75" customHeight="1">
       <c r="B186" s="18" t="s">
         <v>39</v>
       </c>
@@ -3153,16 +3147,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" ht="15.75" customHeight="1">
       <c r="C187" s="8"/>
     </row>
-    <row r="188">
+    <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="6" t="s">
         <v>80</v>
       </c>
       <c r="C188" s="8"/>
     </row>
-    <row r="189">
+    <row r="189" ht="15.75" customHeight="1">
       <c r="B189" s="6" t="s">
         <v>11</v>
       </c>
@@ -3170,7 +3164,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" ht="15.75" customHeight="1">
       <c r="B190" s="6" t="s">
         <v>13</v>
       </c>
@@ -3178,7 +3172,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" ht="15.75" customHeight="1">
       <c r="B191" s="6" t="s">
         <v>2</v>
       </c>
@@ -3186,13 +3180,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" ht="15.75" customHeight="1">
       <c r="B192" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C192" s="7"/>
     </row>
-    <row r="193">
+    <row r="193" ht="15.75" customHeight="1">
       <c r="B193" s="6" t="s">
         <v>15</v>
       </c>
@@ -3200,7 +3194,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" ht="15.75" customHeight="1">
       <c r="B194" s="10" t="s">
         <v>37</v>
       </c>
@@ -3208,7 +3202,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" ht="15.75" customHeight="1">
       <c r="B195" s="18" t="s">
         <v>39</v>
       </c>
@@ -3216,16 +3210,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" ht="15.75" customHeight="1">
       <c r="C196" s="8"/>
     </row>
-    <row r="197">
+    <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="6" t="s">
         <v>84</v>
       </c>
       <c r="C197" s="8"/>
     </row>
-    <row r="198">
+    <row r="198" ht="15.75" customHeight="1">
       <c r="B198" s="6" t="s">
         <v>11</v>
       </c>
@@ -3233,7 +3227,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" ht="15.75" customHeight="1">
       <c r="B199" s="6" t="s">
         <v>13</v>
       </c>
@@ -3241,7 +3235,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" ht="15.75" customHeight="1">
       <c r="B200" s="6" t="s">
         <v>2</v>
       </c>
@@ -3249,13 +3243,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" ht="15.75" customHeight="1">
       <c r="B201" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C201" s="7"/>
     </row>
-    <row r="202">
+    <row r="202" ht="15.75" customHeight="1">
       <c r="B202" s="6" t="s">
         <v>15</v>
       </c>
@@ -3263,7 +3257,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" ht="15.75" customHeight="1">
       <c r="B203" s="10" t="s">
         <v>37</v>
       </c>
@@ -3271,7 +3265,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" ht="15.75" customHeight="1">
       <c r="B204" s="18" t="s">
         <v>39</v>
       </c>
